--- a/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
+++ b/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>А-376</t>
+          <t>ЛК-670</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,40 +475,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Подробность механический трясти тусклый лететь помолчать спичка.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Исакова С.Ф.</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ЛК977</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -516,23 +518,21 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Борисов П.И.</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ГУ-164</t>
+          <t>ГУ-276</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -553,17 +553,15 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ЛК-951</t>
+          <t>А-712</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -572,33 +570,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Приходить возникновение счастье выраженный доставать граница за.</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ЛК-154</t>
+          <t>А329</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -607,7 +601,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -615,25 +609,25 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Медведева С.Ж.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ЦИТ-386</t>
+          <t>ГУ-915</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,33 +636,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Рота подробность вздрогнуть космос.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Капустин В.А.</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ГУ-480</t>
+          <t>А143</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,42 +671,38 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Добиться налево палка правление.</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЛК-162</t>
+          <t>А143</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -721,28 +711,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Фонарик предоставить коричневый постоянный.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Брагин П.Г.</t>
-        </is>
-      </c>
+          <t>25 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЛК435</t>
+          <t>ПА-223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +737,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -767,13 +753,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>А-992</t>
+          <t>ЛК698</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -782,37 +768,29 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Социалистический даль поставить правление устройство ягода кузнец намерение.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Антонов М.Ф.</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ПА-972</t>
+          <t>ПА-813</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -821,23 +799,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Светило вскинуть построить металл.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Щукина М.А.</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
@@ -845,13 +815,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>А846</t>
+          <t>ЛК-964</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -860,7 +830,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -876,22 +846,22 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ПА-768</t>
+          <t>ГУ-734</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -900,24 +870,20 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ПА-900</t>
+          <t>ЛК-347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -926,7 +892,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -948,38 +914,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>ГУ-915</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ПК (6 шт), TV</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ПА-515</t>
+          <t>А963</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -988,7 +958,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -997,18 +967,24 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ГУ500</t>
+          <t>ЦИТ-754</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1017,7 +993,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1028,7 +1004,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1036,12 +1012,14 @@
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>А954</t>
+          <t>ГУ-815</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1050,33 +1028,29 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Тысяча июнь помолчать картинка страсть.</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>А846</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1085,7 +1059,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1094,42 +1068,46 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>А692</t>
+          <t>ЛК-523</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Разуметься бетонный какой песня казнь.</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
@@ -1142,16 +1120,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>А212</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1160,24 +1138,28 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Освободить пропадать сомнительный интеллектуальный девка передо спалить.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>ЦИТ-329</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1186,7 +1168,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1194,69 +1176,63 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Евсеева Х.В.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>А161</t>
+          <t>ЛК-347</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Деньги ленинград песня витрина стакан.</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>А692</t>
+          <t>ПА-461</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1265,28 +1241,28 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Моноблок (14 шт), TV</t>
+          <t>Отметить единый полевой чем спалить ботинок.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Захаров М.Я.</t>
+          <t>Петухов И.Н.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ЛК-768</t>
+          <t>А305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1295,81 +1271,73 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Инфекция четыре радость неправда ярко зима строительство.</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ЛК821</t>
+          <t>ПА-157</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Моноблок (10 шт), TV</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>А-235</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5000</v>
+        <v>132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1378,24 +1346,18 @@
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ЛК-458</t>
+          <t>ГУ887</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1404,7 +1366,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1416,17 +1378,17 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ЛК513</t>
+          <t>А-282</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1435,7 +1397,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1443,30 +1405,32 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Михеева Е.В.</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>8</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ЛК-111</t>
+          <t>ЛК913</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>36</v>
+        <v>800</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1474,41 +1438,41 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Беспалова С.Ю.</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>А934</t>
+          <t>ЛК545</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Кожа вообще нажать грудь.</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
@@ -1517,13 +1481,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ГУ-725</t>
+          <t>ЛК-442</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1532,7 +1496,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1548,13 +1512,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>А951</t>
+          <t>ПА-967</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1563,7 +1527,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1572,113 +1536,115 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Отъезд способ коммунизм сопровождаться коммунизм решение пространство.</t>
+          <t>Цвет потом слишком социалистический.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>А975</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>132</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ЛК932</t>
+          <t>ЛК836</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>21 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ЦИТ-687</t>
+          <t>ЛК626</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>23 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>А-956</t>
+          <t>ПА-783</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1687,7 +1653,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1696,14 +1662,10 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Петухов К.А.</t>
-        </is>
-      </c>
+          <t>19 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
@@ -1711,13 +1673,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ЦИТ-169</t>
+          <t>ГУ266</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1726,7 +1688,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1735,20 +1697,24 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ЛК-514</t>
+          <t>ЦИТ-687</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1757,7 +1723,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1765,25 +1731,23 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ларионов Р.А.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>4</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ГУ-519</t>
+          <t>ПА-289</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1792,37 +1756,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Ботинок аллея проход девка.</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>А627</t>
+          <t>ЦИТ-218</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1831,7 +1791,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1840,28 +1800,28 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21 ПК, TV</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>А846</t>
+          <t>А975</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1870,7 +1830,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1882,17 +1842,17 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ЛК-162</t>
+          <t>А642</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1901,7 +1861,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1913,7 +1873,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -1923,7 +1883,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ЦИТ-501</t>
+          <t>ПА-547</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1932,7 +1892,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1944,26 +1904,26 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ЛК121</t>
+          <t>ГУ-171</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1972,24 +1932,20 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>А889</t>
+          <t>ЛК896</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1998,7 +1954,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2007,53 +1963,59 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ЛК-514</t>
+          <t>ГУ760</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20 ПК, TV</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ЛК539</t>
+          <t>ПА-311</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2074,38 +2036,46 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>А889</t>
+          <t>А143</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2115,16 +2085,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ЦИТ-527</t>
+          <t>А-133</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2136,46 +2106,36 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ГУ588</t>
+          <t>ЛК108</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Рассуждение горький конференция руководитель металл ведь.</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -2185,7 +2145,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>ГУ-371</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2194,7 +2154,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2209,34 +2169,28 @@
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>6</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>А794</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ПК (13 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
@@ -2244,14 +2198,12 @@
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>3</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ГУ698</t>
+          <t>ПА-159</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2260,7 +2212,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2271,22 +2223,22 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ПА-934</t>
+          <t>ЦИТ-754</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2295,7 +2247,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2303,15 +2255,15 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Мельников В.Д.</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2319,7 +2271,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ЛК513</t>
+          <t>ЦИТ-946</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2328,7 +2280,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2340,79 +2292,67 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>А-954</t>
+          <t>ПА-259</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Моноблок (7 шт), экран</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ЦИТ-687</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>176</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1</v>
-      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>А182</t>
+          <t>ЛК184</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2421,7 +2361,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2433,38 +2373,46 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ПА-697</t>
+          <t>А-276</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>18 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Одинцов А.А.</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -2474,7 +2422,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ЛК634</t>
+          <t>ГУ-574</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2483,7 +2431,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2492,18 +2440,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Моноблок (5 шт), проектор</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Большаков В.Ф.</t>
-        </is>
-      </c>
+          <t>ПК (12 шт), проектор</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -2511,32 +2455,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>А-532</t>
+          <t>А-260</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>17 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -2546,7 +2490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ГУ217</t>
+          <t>ЛК-523</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2564,137 +2508,105 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>15 ПК, TV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ГУ698</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Компьютерный класс</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>16</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>15 ПК, TV</t>
-        </is>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>А695</t>
+          <t>ГУ-734</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>11 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>А692</t>
+          <t>ЦИТ-757</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ПК (12 шт), TV</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ЛК634</t>
+          <t>ГУ-562</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2703,7 +2615,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2712,24 +2624,20 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ЛК283</t>
+          <t>ЛК562</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2738,7 +2646,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2750,17 +2658,17 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ЛК-852</t>
+          <t>ЦИТ-946</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2769,7 +2677,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2781,26 +2689,24 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>А-581</t>
+          <t>ПА-967</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2809,103 +2715,97 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ГУ415</t>
+          <t>А145</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>21 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>А227</t>
+          <t>ЛК-187</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>5</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ЛК-281</t>
+          <t>ЛК368</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2914,33 +2814,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Виднеться исследование поезд порядок.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ЛК435</t>
+          <t>ГУ-610</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2949,7 +2849,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19 ПК, TV</t>
+          <t>Умирать шлем мелькнуть развитый намерение предоставить бетонный ночь.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -2960,22 +2860,22 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>А975</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2984,18 +2884,24 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ЦИТ-401</t>
+          <t>ЛК746</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3004,7 +2910,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3012,28 +2918,34 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Кабанова А.Г.</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>А-846</t>
+          <t>ЛК-817</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3042,24 +2954,18 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>5</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ГУ645</t>
+          <t>ПА-727</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3068,7 +2974,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3077,14 +2983,10 @@
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3092,27 +2994,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>А975</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>12 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
@@ -3121,13 +3019,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ГУ-951</t>
+          <t>А890</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3136,7 +3034,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3146,17 +3044,13 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Красильников Л.Ф.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+          <t>Большаков Л.Р.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3164,38 +3058,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ЦИТ-561</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>20</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>4</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ЦИТ-653</t>
+          <t>ГУ-568</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3204,7 +3082,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3213,25 +3091,29 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>А951</t>
+          <t>ЛК-197</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -3244,24 +3126,28 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>18 ПК, TV</t>
+          <t>Моноблок (7 шт), экран</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ЦИТ-527</t>
+          <t>А963</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3270,7 +3156,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3286,13 +3172,13 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ЛК-281</t>
+          <t>ЛК-590</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3313,17 +3199,17 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>А-956</t>
+          <t>А890</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3332,7 +3218,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3341,29 +3227,25 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ЦИТ-681</t>
+          <t>ЛК-187</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3376,55 +3258,55 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>А537</t>
+          <t>А143</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Моноблок (10 шт), TV</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ЛК977</t>
+          <t>А-416</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3433,7 +3315,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3442,59 +3324,59 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>22 ПК, TV</t>
+          <t>18 ПК, TV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ГУ452</t>
+          <t>ЛК898</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>14 ПК, TV</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ПА-634</t>
+          <t>ЛК784</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3503,7 +3385,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3515,61 +3397,57 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ПА-300</t>
+          <t>ПА-470</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>19 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>А-750</t>
+          <t>ГУ645</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3581,17 +3459,15 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>7</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ЛК-281</t>
+          <t>ГУ-915</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3600,7 +3476,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3609,7 +3485,11 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
@@ -3622,16 +3502,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ЦИТ-653</t>
+          <t>ЛК559</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>400</v>
+        <v>26</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3643,17 +3523,17 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ЦИТ-608</t>
+          <t>ЛК-588</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3662,7 +3542,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3671,24 +3551,20 @@
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ПА-235</t>
+          <t>ЦИТ-907</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3697,7 +3573,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3706,24 +3582,28 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Понятный дорогой казнь.</t>
+          <t>Экзамен совет отдел оборот угроза табак блин виднеться.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ГУ707</t>
+          <t>ЛК-442</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3732,7 +3612,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3741,101 +3621,121 @@
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ЛК121</t>
+          <t>ЦИТ-822</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>23 ПК, TV</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>6</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+          <t>ПА-259</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>42</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ЛК932</t>
+          <t>ГУ-610</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>17 ПК, TV</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>А324</t>
+          <t>ЦИТ-757</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3844,7 +3744,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3860,22 +3760,22 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ЛК435</t>
+          <t>ПА-461</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3884,22 +3784,20 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ПА-972</t>
+          <t>ПА-783</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3908,75 +3806,81 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Полюбить собеседник зима механический.</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>А-750</t>
+          <t>ЛК562</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>16 ПК, TV</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ЦИТ-488</t>
+          <t>ЦИТ-791</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3985,13 +3889,13 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ломать налоговый бочок.</t>
+          <t>22 ПК, TV</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4000,13 +3904,13 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ЛК-154</t>
+          <t>ЦИТ-946</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4015,7 +3919,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4031,17 +3935,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>А324</t>
+          <t>ГУ-631</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4050,64 +3954,68 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Какой полевой правление солнце наступать около лапа магазин.</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ГУ698</t>
+          <t>ГУ587</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>ЦИТ-218</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4116,7 +4024,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4125,42 +4033,40 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>17 ПК, TV</t>
+          <t>25 ПК, TV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ГУ-164</t>
+          <t>ГУ587</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Изредка снимать наслаждение девка миг дальний.</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
@@ -4169,13 +4075,13 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ЛК-154</t>
+          <t>А-424</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4184,7 +4090,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4196,17 +4102,17 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>А754</t>
+          <t>ЦИТ-329</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4215,7 +4121,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4223,25 +4129,19 @@
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Корнилова У.Г.</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>5</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ЛК537</t>
+          <t>ЛК559</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4250,7 +4150,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4259,24 +4159,28 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>18 ПК, TV</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>А-235</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4285,7 +4189,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4294,10 +4198,14 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -4305,7 +4213,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ЛК372</t>
+          <t>ГУ-847</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4314,7 +4222,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4322,11 +4230,15 @@
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Маслов В.Е.</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -4336,7 +4248,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>А761</t>
+          <t>А601</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4345,70 +4257,48 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Новый правление степь реклама точно.</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Петухова А.Н.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ЛК223</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>60</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Актриса наступать поймать угроза актриса дыхание.</t>
-        </is>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
-        <v>1</v>
-      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ЛК-752</t>
+          <t>ЛК-181</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4417,7 +4307,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4429,48 +4319,32 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>А-551</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>42</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>6</v>
-      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ГУ500</t>
+          <t>ГУ645</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4479,7 +4353,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4491,17 +4365,15 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>8</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ПА-963</t>
+          <t>ЛК184</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4510,7 +4382,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4519,20 +4391,24 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ЦИТ-801</t>
+          <t>ГУ134</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4541,7 +4417,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4553,7 +4429,7 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -4563,62 +4439,56 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ГУ-395</t>
+          <t>А963</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Владимирова Д.А.</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>25 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>6</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>А-712</t>
+          <t>А-387</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>23 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
@@ -4627,53 +4497,37 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ЛК821</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>48</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I127" t="n">
-        <v>6</v>
-      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ЛК-154</t>
+          <t>ЛК847</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5000</v>
+        <v>40</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4682,10 +4536,14 @@
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -4695,7 +4553,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ЛК977</t>
+          <t>ЛК-817</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4704,33 +4562,27 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Смеяться построить место цепочка разнообразный порода ручей возбуждение.</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I129" t="n">
-        <v>8</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>А761</t>
+          <t>А-276</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4748,29 +4600,33 @@
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>А537</t>
+          <t>А-387</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4779,65 +4635,55 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Моноблок (15 шт), проектор</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ГУ-244</t>
+          <t>ГУ-562</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Михеев П.Д.</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ЛК223</t>
+          <t>ЛК452</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4846,7 +4692,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4854,25 +4700,21 @@
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Логинов И.Г.</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ЦИТ-681</t>
+          <t>ЛК-187</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4881,7 +4723,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4890,22 +4732,20 @@
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ЛК513</t>
+          <t>А-424</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4914,7 +4754,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4922,25 +4762,23 @@
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Капустин Э.К.</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I135" t="n">
-        <v>4</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ГУ707</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4949,29 +4787,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Спичка необычный угроза цель понятный ломать доставать.</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I136" t="n">
-        <v>6</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ЛК547</t>
+          <t>А601</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4980,23 +4820,23 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Актриса плясать тусклый жестокий.</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -5006,7 +4846,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ЦИТ-899</t>
+          <t>ЛК-817</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5015,7 +4855,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -5027,52 +4867,50 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ЦИТ-687</t>
+          <t>ГУ-337</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>800</v>
+        <v>20</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Осипов Н.Г.</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Интеллектуальный труп мера товар падаль пламя.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I139" t="n">
-        <v>1</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ПА-515</t>
+          <t>ЛК746</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5081,7 +4919,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5090,24 +4928,20 @@
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ЦИТ-386</t>
+          <t>ЦИТ-791</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5116,7 +4950,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5125,24 +4959,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Моноблок (13 шт), проектор</t>
+          <t>Моноблок (8 шт), TV</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ЛК-315</t>
+          <t>ПА-813</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5151,7 +4985,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5163,37 +4997,33 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ЦИТ-899</t>
+          <t>ЦИТ-511</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>15 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
@@ -5202,13 +5032,13 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>А-818</t>
+          <t>ЛК896</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5217,7 +5047,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5226,24 +5056,20 @@
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ЛК340</t>
+          <t>ГУ103</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5252,7 +5078,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5260,15 +5086,15 @@
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Морозов П.Е.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -5276,16 +5102,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ЦИТ-681</t>
+          <t>ГУ577</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5294,93 +5120,107 @@
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>А-416</t>
+          <t>ПА-518</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>25 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Мухин С.Т.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>А-818</t>
+          <t>ПА-311</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>11 ПК, TV</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ПА-152</t>
+          <t>А-697</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5392,17 +5232,17 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ГУ330</t>
+          <t>ЛК452</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5411,7 +5251,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5419,25 +5259,21 @@
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Горбунова Б.Х.</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>А-376</t>
+          <t>ПА-219</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5446,7 +5282,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5455,14 +5291,10 @@
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -5470,12 +5302,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ЛК-514</t>
+          <t>ЛК698</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -5486,11 +5318,7 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Появление вздрагивать приходить секунда новый голубчик.</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
@@ -5498,49 +5326,43 @@
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>5</v>
-      </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>А846</t>
+          <t>ЛК562</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>16 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ЛК932</t>
+          <t>ГУ-602</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5549,37 +5371,33 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Ночь иной заведение инвалид.</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Муравьев Г.В.</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ЛК-852</t>
+          <t>А-424</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5588,7 +5406,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5596,23 +5414,21 @@
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Петров И.Е.</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ЛК-252</t>
+          <t>ГУ-847</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5621,7 +5437,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5633,17 +5449,17 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>А754</t>
+          <t>ЦИТ-144</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5652,7 +5468,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5661,14 +5477,10 @@
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -5678,73 +5490,85 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ЦИТ-681</t>
+          <t>ЦИТ-754</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Павлов Н.А.</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>23 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ГУ472</t>
+          <t>ГУ760</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>18 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Гущин Ю.В.</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ЛК539</t>
+          <t>А-697</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5753,7 +5577,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5765,17 +5589,15 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>8</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>А182</t>
+          <t>ПА-228</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5784,7 +5606,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5793,24 +5615,20 @@
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>ПА-727</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5819,7 +5637,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5831,17 +5649,17 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ЛК-162</t>
+          <t>ЦИТ-218</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5850,7 +5668,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5858,11 +5676,7 @@
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Кузьмина П.А.</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
@@ -5874,16 +5688,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>А-711</t>
+          <t>ГУ576</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -5892,14 +5706,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>24 ПК, TV</t>
+          <t>О роскошный призыв потянуться инвалид плавно самостоятельно.</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -5907,16 +5721,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ЦИТ-561</t>
+          <t>ГУ580</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -5928,17 +5742,17 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>ПА-303</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5947,7 +5761,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5959,54 +5773,46 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ГУ211</t>
+          <t>ЛК-327</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>21 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
-        <v>7</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>А324</t>
+          <t>ЛК184</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6015,7 +5821,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -6024,24 +5830,28 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>19 ПК, TV</t>
+          <t>20 ПК, TV</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ГУ-951</t>
+          <t>ЛК339</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6050,7 +5860,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6065,39 +5875,37 @@
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>4</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>А295</t>
+          <t>ЛК530</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>16 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -6105,32 +5913,28 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ЦИТ-487</t>
+          <t>ЛК-402</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>16 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -6140,60 +5944,54 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ПА-889</t>
+          <t>А329</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Моноблок (6 шт), TV</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ГУ594</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Моноблок (5 шт), экран</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
@@ -6202,13 +6000,13 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>А846</t>
+          <t>ГУ-171</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6217,7 +6015,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6228,31 +6026,31 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ПА-462</t>
+          <t>ЛК368</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>800</v>
+        <v>192</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6264,24 +6062,26 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ЛК537</t>
+          <t>ЛК836</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>16</v>
+        <v>5000</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6293,54 +6093,52 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ПА-246</t>
+          <t>ЛК368</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>ПК (11 шт), TV</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ГУ330</t>
+          <t>ЦИТ-218</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6349,7 +6147,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6358,22 +6156,20 @@
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ЛК-610</t>
+          <t>А143</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6382,7 +6178,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6391,94 +6187,68 @@
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>6</v>
-      </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ПА-515</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>100</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>6</v>
-      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ЛК748</t>
+          <t>ПА-219</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ЛК-498</t>
+          <t>А329</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6487,18 +6257,14 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Бочок а социалистический пробовать возможно школьный способ.</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
@@ -6507,13 +6273,13 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ЦИТ-192</t>
+          <t>ГУ103</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6522,7 +6288,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6531,20 +6297,24 @@
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ЛК-610</t>
+          <t>ЛК-122</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6553,7 +6323,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6565,24 +6335,26 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ЛК-458</t>
+          <t>ЛК-590</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6591,33 +6363,37 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Бегать тревога мелочь полностью освобождение тысяча помолчать возможно.</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Белозеров Э.Б.</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ПА-515</t>
+          <t>ГУ505</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6626,26 +6402,28 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Пол дошлый угодный поговорить цель необычный.</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>А-371</t>
+          <t>ПА-259</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6666,26 +6444,26 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ЛК121</t>
+          <t>ГУ-371</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -6694,10 +6472,14 @@
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -6707,7 +6489,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ЦИТ-653</t>
+          <t>ГУ467</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6716,33 +6498,29 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Актриса затянуться порядок освобождение зачем.</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ГУ-592</t>
+          <t>ГУ817</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6751,7 +6529,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -6760,63 +6538,61 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Моноблок (7 шт), экран</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Дорофеева И.А.</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr"/>
+          <t>Моноблок (8 шт), проектор</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>5</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ГУ415</t>
+          <t>ГУ-276</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>ПК (5 шт), проектор</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Дьячкова П.А.</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>А-376</t>
+          <t>А-813</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6825,7 +6601,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -6834,14 +6610,10 @@
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -6851,69 +6623,77 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ПА-246</t>
+          <t>ПА-354</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Смеяться ложиться полюбить развитый.</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ЛК-752</t>
+          <t>ЦИТ-791</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>19 ПК, TV</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ЛК525</t>
+          <t>ПА-303</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6922,7 +6702,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -6930,85 +6710,81 @@
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Михайлова Т.Э.</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ПА-697</t>
+          <t>ЛК452</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>11 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>А-551</t>
+          <t>ЛК-964</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -7016,7 +6792,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>А652</t>
+          <t>ГУ817</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7025,7 +6801,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7040,14 +6816,12 @@
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>2</v>
-      </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ГУ-725</t>
+          <t>ЛК452</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7056,7 +6830,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7076,83 +6850,63 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ПА-405</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Общего назначения</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>18</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I200" t="n">
-        <v>1</v>
-      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ПА-235</t>
+          <t>А-372</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>19 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ГУ-164</t>
+          <t>ЛК-402</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7161,7 +6915,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7173,75 +6927,296 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>А889</t>
+          <t>А422</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>15 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ПА-246</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>70</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr">
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>А-372</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Общего назначения</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>16</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ЦИТ-757</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>100</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Проход тута ручей прежде тяжелый эпоха жестокий слишком.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ГУ134</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>100</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ЛК-402</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>25</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>24 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>А-424</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>40</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I204" t="n">
+      <c r="I209" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ГУ817</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Лаборатория</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>16</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Моноблок (10 шт), TV</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ГУ-455</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>200</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
